--- a/data/trans_camb/IP1001-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP1001-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,55; -0,61</t>
+          <t>-5,6; -0,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 3,25</t>
+          <t>-3,59; 3,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 5,48</t>
+          <t>-2,37; 5,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 5,37</t>
+          <t>-0,63; 5,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,14; 7,1</t>
+          <t>0,17; 6,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 14,38</t>
+          <t>-0,63; 13,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 0,96</t>
+          <t>-2,32; 1,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 3,8</t>
+          <t>-0,87; 4,15</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 6,77</t>
+          <t>-0,56; 6,85</t>
         </is>
       </c>
     </row>
@@ -788,12 +788,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 563,9</t>
+          <t>-100,0; 653,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-68,38; 829,26</t>
+          <t>-76,88; 723,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-55,14; 561,14</t>
+          <t>-43,69; 712,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-58,76; 1085,85</t>
+          <t>-50,76; 1132,3</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,38; 0,28</t>
+          <t>-7,93; 0,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,62; -1,5</t>
+          <t>-9,3; -1,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 3,16</t>
+          <t>-6,48; 2,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 2,85</t>
+          <t>-4,83; 2,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 3,14</t>
+          <t>-3,65; 3,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 6,97</t>
+          <t>-2,31; 8,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 0,92</t>
+          <t>-4,51; 0,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 0,15</t>
+          <t>-5,06; 0,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 3,95</t>
+          <t>-3,07; 3,62</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 107,18</t>
+          <t>-100,0; 66,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 223,93</t>
+          <t>-100,0; 191,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-99,74; 366,3</t>
+          <t>-79,05; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-88,16; 66,33</t>
+          <t>-88,81; 69,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-89,19; 43,96</t>
+          <t>-88,77; 32,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-62,59; 208,58</t>
+          <t>-69,62; 217,47</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,05; 0,79</t>
+          <t>-7,76; 0,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 3,65</t>
+          <t>-6,12; 3,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 2,6</t>
+          <t>-5,52; 3,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,3; -1,54</t>
+          <t>-10,29; -1,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,9; 3,74</t>
+          <t>-7,25; 3,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,63; -1,82</t>
+          <t>-10,89; -1,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,08; -1,67</t>
+          <t>-7,67; -1,5</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 1,91</t>
+          <t>-5,16; 2,28</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-7,66; -1,26</t>
+          <t>-7,06; -0,96</t>
         </is>
       </c>
     </row>
@@ -1230,32 +1230,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 23,69</t>
+          <t>-100,0; 132,09</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-81,81; 113,47</t>
+          <t>-81,49; 121,07</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 2,34</t>
+          <t>-100,0; 9,44</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -30,42</t>
+          <t>-100,0; -1,4</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-81,21; 69,14</t>
+          <t>-75,51; 90,75</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 4,01</t>
+          <t>-100,0; -0,58</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 4,03</t>
+          <t>-1,38; 3,87</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 1,68</t>
+          <t>-2,84; 1,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 2,74</t>
+          <t>-2,39; 2,89</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 3,5</t>
+          <t>-1,57; 3,41</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 1,81</t>
+          <t>-2,77; 1,94</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 4,73</t>
+          <t>-0,78; 4,92</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 2,92</t>
+          <t>-0,65; 2,81</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 1,14</t>
+          <t>-1,97; 1,22</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 3,01</t>
+          <t>-0,79; 2,91</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-49,62; 444,69</t>
+          <t>-50,17; 397,27</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-84,16; 193,31</t>
+          <t>-80,04; 260,24</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-71,87; 248,25</t>
+          <t>-69,75; 293,27</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-50,65; 259,46</t>
+          <t>-50,47; 276,87</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-74,7; 165,97</t>
+          <t>-80,43; 175,11</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-34,38; 379,98</t>
+          <t>-30,06; 359,28</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-31,69; 191,99</t>
+          <t>-23,88; 185,03</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-63,33; 80,18</t>
+          <t>-61,36; 93,45</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-34,3; 195,6</t>
+          <t>-33,74; 196,98</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 1,7</t>
+          <t>-6,56; 1,58</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 3,32</t>
+          <t>-5,41; 3,69</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,98; -0,14</t>
+          <t>-7,41; 0,1</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 4,08</t>
+          <t>-2,79; 3,89</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 3,67</t>
+          <t>-3,33; 3,62</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 3,09</t>
+          <t>-3,12; 3,16</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 1,57</t>
+          <t>-3,35; 1,84</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 2,38</t>
+          <t>-2,94; 2,62</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 0,79</t>
+          <t>-4,14; 0,62</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-85,97; 138,95</t>
+          <t>-86,24; 114,8</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-80,16; 134,3</t>
+          <t>-76,99; 158,51</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 40,38</t>
+          <t>-100,0; 100,0</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-79,58; 443,12</t>
+          <t>-71,82; 376,01</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-75,07; 384,95</t>
+          <t>-77,97; 327,73</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-81,06; 293,33</t>
+          <t>-79,5; 304,59</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-68,86; 72,0</t>
+          <t>-68,32; 90,2</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-59,99; 114,68</t>
+          <t>-61,62; 118,03</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-77,3; 37,45</t>
+          <t>-80,21; 39,7</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 0,0</t>
+          <t>-7,36; 0,0</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 7,18</t>
+          <t>-3,21; 6,82</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-7,21; 0,58</t>
+          <t>-6,37; 0,58</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 4,78</t>
+          <t>-1,81; 4,6</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 3,28</t>
+          <t>-1,82; 3,34</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,47; 11,77</t>
+          <t>0,38; 12,2</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 1,63</t>
+          <t>-2,91; 2,04</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 3,61</t>
+          <t>-1,54; 4,05</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 5,97</t>
+          <t>-1,34; 5,04</t>
         </is>
       </c>
     </row>
@@ -1898,12 +1898,12 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-82,47; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-76,86; 1675,29</t>
+          <t>-78,52; 1052,09</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 0,39</t>
+          <t>-2,42; 0,49</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 0,59</t>
+          <t>-2,24; 0,73</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 0,69</t>
+          <t>-2,2; 0,7</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 1,17</t>
+          <t>-1,44; 1,23</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 1,44</t>
+          <t>-1,39; 1,42</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 3,0</t>
+          <t>-0,43; 3,2</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 0,31</t>
+          <t>-1,68; 0,32</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 0,51</t>
+          <t>-1,43; 0,54</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 1,39</t>
+          <t>-0,96; 1,53</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-65,64; 18,81</t>
+          <t>-64,74; 30,94</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-60,68; 33,81</t>
+          <t>-60,45; 32,4</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-58,76; 39,19</t>
+          <t>-59,91; 34,93</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-47,06; 60,47</t>
+          <t>-44,79; 61,54</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-38,7; 76,57</t>
+          <t>-40,6; 72,91</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-26,91; 147,71</t>
+          <t>-15,44; 152,14</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-48,28; 14,42</t>
+          <t>-49,81; 14,22</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-40,96; 22,51</t>
+          <t>-42,25; 26,23</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-31,0; 59,72</t>
+          <t>-29,77; 65,83</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1001-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP1001-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,6; -0,67</t>
+          <t>-5,81; -0,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 3,27</t>
+          <t>-3,52; 3,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 5,12</t>
+          <t>-2,13; 5,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 5,03</t>
+          <t>-0,63; 4,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 6,99</t>
+          <t>0,09; 7,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 13,8</t>
+          <t>-0,63; 11,11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 1,31</t>
+          <t>-2,28; 1,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 4,15</t>
+          <t>-0,88; 4,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 6,85</t>
+          <t>-0,6; 7,08</t>
         </is>
       </c>
     </row>
@@ -788,12 +788,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 653,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-76,88; 723,45</t>
+          <t>-65,46; 775,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-43,69; 712,98</t>
+          <t>-49,42; 581,12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-50,76; 1132,3</t>
+          <t>-57,98; 828,41</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,93; 0,06</t>
+          <t>-8,24; 0,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,3; -1,99</t>
+          <t>-9,27; -1,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 2,52</t>
+          <t>-6,29; 2,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 2,74</t>
+          <t>-4,78; 2,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 3,62</t>
+          <t>-3,83; 3,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 8,45</t>
+          <t>-2,33; 8,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 0,75</t>
+          <t>-4,64; 0,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 0,16</t>
+          <t>-4,92; 0,06</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 3,62</t>
+          <t>-2,92; 3,83</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 66,23</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 191,03</t>
+          <t>-100,0; 261,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1019,27 +1019,27 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-79,05; —</t>
+          <t>-84,24; 651,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-77,53; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-88,81; 69,05</t>
+          <t>-89,34; 49,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-88,77; 32,56</t>
+          <t>-89,2; 20,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-69,62; 217,47</t>
+          <t>-66,46; 239,89</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 0,8</t>
+          <t>-7,61; 0,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 3,34</t>
+          <t>-5,92; 3,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 3,21</t>
+          <t>-5,91; 3,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,29; -1,6</t>
+          <t>-10,66; -1,74</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 3,6</t>
+          <t>-7,14; 3,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,89; -1,87</t>
+          <t>-10,82; -1,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,67; -1,5</t>
+          <t>-7,53; -1,36</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 2,28</t>
+          <t>-5,3; 2,34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-7,06; -0,96</t>
+          <t>-7,0; -0,7</t>
         </is>
       </c>
     </row>
@@ -1230,32 +1230,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 132,09</t>
+          <t>-100,0; 30,71</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-81,49; 121,07</t>
+          <t>-84,77; 109,92</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 9,44</t>
+          <t>-100,0; 76,07</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -1,4</t>
+          <t>-100,0; -17,94</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-75,51; 90,75</t>
+          <t>-77,58; 98,57</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -0,58</t>
+          <t>-100,0; 11,47</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 3,87</t>
+          <t>-1,19; 4,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 1,87</t>
+          <t>-2,79; 1,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 2,89</t>
+          <t>-2,24; 3,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 3,41</t>
+          <t>-1,73; 3,56</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 1,94</t>
+          <t>-2,39; 2,21</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 4,92</t>
+          <t>-1,09; 4,77</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 2,81</t>
+          <t>-0,65; 2,85</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 1,22</t>
+          <t>-1,94; 1,08</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 2,91</t>
+          <t>-0,76; 3,21</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-50,17; 397,27</t>
+          <t>-40,17; 413,3</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-80,04; 260,24</t>
+          <t>-79,18; 179,99</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-69,75; 293,27</t>
+          <t>-69,61; 319,52</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-50,47; 276,87</t>
+          <t>-51,43; 286,97</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-80,43; 175,11</t>
+          <t>-72,97; 204,55</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-30,06; 359,28</t>
+          <t>-36,79; 385,56</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-23,88; 185,03</t>
+          <t>-26,44; 199,02</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-61,36; 93,45</t>
+          <t>-62,56; 81,73</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-33,74; 196,98</t>
+          <t>-28,36; 215,81</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 1,58</t>
+          <t>-6,97; 1,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 3,69</t>
+          <t>-5,89; 3,14</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 0,1</t>
+          <t>-8,02; -0,41</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 3,89</t>
+          <t>-2,88; 3,87</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 3,62</t>
+          <t>-2,81; 3,57</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 3,16</t>
+          <t>-3,32; 3,38</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 1,84</t>
+          <t>-3,52; 1,71</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 2,62</t>
+          <t>-2,5; 2,91</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 0,62</t>
+          <t>-4,05; 0,94</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-86,24; 114,8</t>
+          <t>-90,78; 53,49</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-76,99; 158,51</t>
+          <t>-83,49; 122,67</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 100,0</t>
+          <t>-100,0; 94,44</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-71,82; 376,01</t>
+          <t>-74,04; 418,77</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-77,97; 327,73</t>
+          <t>-71,08; 421,85</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-79,5; 304,59</t>
+          <t>-82,22; 332,62</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-68,32; 90,2</t>
+          <t>-68,65; 89,61</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-61,62; 118,03</t>
+          <t>-55,1; 161,69</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-80,21; 39,7</t>
+          <t>-79,92; 52,27</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-7,36; 0,0</t>
+          <t>-7,3; 0,0</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 6,82</t>
+          <t>-2,96; 6,91</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 0,58</t>
+          <t>-6,15; 0,58</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 4,6</t>
+          <t>-1,82; 4,72</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 3,34</t>
+          <t>-1,82; 3,39</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,38; 12,2</t>
+          <t>0,94; 12,67</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 2,04</t>
+          <t>-3,04; 1,59</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 4,05</t>
+          <t>-1,94; 3,69</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 5,04</t>
+          <t>-1,32; 5,53</t>
         </is>
       </c>
     </row>
@@ -1898,12 +1898,12 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-87,39; 756,45</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-78,52; 1052,09</t>
+          <t>-100,0; 928,13</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 0,49</t>
+          <t>-2,49; 0,24</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 0,73</t>
+          <t>-2,31; 0,47</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 0,7</t>
+          <t>-2,4; 0,57</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 1,23</t>
+          <t>-1,66; 1,21</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 1,42</t>
+          <t>-1,31; 1,45</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 3,2</t>
+          <t>-0,65; 3,0</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 0,32</t>
+          <t>-1,62; 0,25</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 0,54</t>
+          <t>-1,36; 0,66</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 1,53</t>
+          <t>-0,89; 1,31</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-64,74; 30,94</t>
+          <t>-64,76; 14,0</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-60,45; 32,4</t>
+          <t>-61,14; 23,54</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-59,91; 34,93</t>
+          <t>-61,41; 29,86</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-44,79; 61,54</t>
+          <t>-48,2; 61,32</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-40,6; 72,91</t>
+          <t>-39,94; 74,22</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-15,44; 152,14</t>
+          <t>-21,24; 151,54</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-49,81; 14,22</t>
+          <t>-48,68; 8,92</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-42,25; 26,23</t>
+          <t>-41,46; 29,76</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-29,77; 65,83</t>
+          <t>-28,58; 59,73</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1001-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP1001-Clase-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,12</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2,87</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,89</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-2,38</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-0,23</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,17</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,12</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,87</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,62</t>
+          <t>1,51</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,85</t>
+          <t>1,07</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,81; -0,61</t>
+          <t>-0,73; 5,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 3,39</t>
+          <t>0,14; 7,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 5,68</t>
+          <t>-1,16; 3,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 4,64</t>
+          <t>-5,55; -0,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,09; 7,07</t>
+          <t>-3,14; 3,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 11,11</t>
+          <t>-1,87; 6,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 1,14</t>
+          <t>-2,68; 0,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 4,09</t>
+          <t>-0,98; 3,8</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 7,08</t>
+          <t>-1,1; 3,58</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>177,67%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>454,66%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>141,91%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-9,57%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>49,33%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>177,67%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>454,66%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>415,69%</t>
+          <t>63,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>120,41%</t>
+          <t>69,68%</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-65,46; 775,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -803,27 +803,27 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 563,9</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>-65,0; 964,87</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-49,42; 581,12</t>
+          <t>-55,14; 561,14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-57,98; 828,41</t>
+          <t>-57,31; 639,67</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,46</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,13</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2,23</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-3,1</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-4,4</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,82</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,46</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,13</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,93</t>
+          <t>-1,69</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,23</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,24; 0,08</t>
+          <t>-4,6; 2,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,27; -1,49</t>
+          <t>-4,12; 3,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 2,91</t>
+          <t>-2,54; 7,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 2,8</t>
+          <t>-8,38; 0,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 3,36</t>
+          <t>-9,62; -1,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 8,94</t>
+          <t>-6,31; 3,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 0,63</t>
+          <t>-4,54; 0,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 0,06</t>
+          <t>-5,22; 0,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 3,83</t>
+          <t>-2,84; 4,27</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-17,75%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4,95%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>85,9%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-70,53%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-41,25%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-17,75%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4,95%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>-38,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -1004,42 +1004,42 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>-99,74; 366,3</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 261,95</t>
-        </is>
-      </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 107,18</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-84,24; 651,17</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-77,53; —</t>
+          <t>-97,27; 243,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-89,34; 49,02</t>
+          <t>-88,16; 66,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-89,2; 20,43</t>
+          <t>-89,19; 43,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-66,46; 239,89</t>
+          <t>-60,39; 221,75</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-5,37</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-1,72</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-5,3</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-2,21</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-0,87</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-1,5</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-5,37</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-1,72</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-5,41</t>
+          <t>-1,48</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-3,8</t>
+          <t>-3,71</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 0,56</t>
+          <t>-10,3; -1,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 3,31</t>
+          <t>-6,9; 3,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 3,05</t>
+          <t>-10,52; -1,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,66; -1,74</t>
+          <t>-7,05; 0,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 3,66</t>
+          <t>-5,28; 3,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,82; -1,85</t>
+          <t>-5,27; 2,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,53; -1,36</t>
+          <t>-8,08; -1,67</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 2,34</t>
+          <t>-5,62; 1,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-7,0; -0,7</t>
+          <t>-7,58; -1,06</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-86,31%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-27,7%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-85,21%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-73,25%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-28,93%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-49,84%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-86,31%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-27,7%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-86,84%</t>
+          <t>-49,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-77,08%</t>
+          <t>-75,36%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 23,69</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>-81,81; 113,47</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>-100,0; 16,81</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 30,71</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-84,77; 109,92</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 76,07</t>
-        </is>
-      </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -17,94</t>
+          <t>-100,0; -30,42</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-77,58; 98,57</t>
+          <t>-81,21; 69,14</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 11,47</t>
+          <t>-100,0; 10,9</t>
         </is>
       </c>
     </row>
@@ -1272,47 +1272,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,9</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,38</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1,91</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>1,25</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-0,37</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,23</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,9</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,8</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,07</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>-0,38</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,71</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,07</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-0,38</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,97</t>
+          <t>1,39</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 4,45</t>
+          <t>-1,64; 3,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 1,75</t>
+          <t>-2,55; 1,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 3,13</t>
+          <t>-0,94; 5,06</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 3,56</t>
+          <t>-1,48; 4,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 2,21</t>
+          <t>-2,77; 1,68</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 4,77</t>
+          <t>-1,75; 3,74</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 2,85</t>
+          <t>-0,94; 2,92</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 1,08</t>
+          <t>-1,94; 1,14</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 3,21</t>
+          <t>-0,52; 3,56</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>37,5%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-16,02%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>79,59%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>57,9%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-17,16%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>10,88%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>37,5%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-16,02%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>61,28%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-40,17; 413,3</t>
+          <t>-50,65; 259,46</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-79,18; 179,99</t>
+          <t>-74,7; 165,97</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-69,61; 319,52</t>
+          <t>-33,87; 392,63</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-51,43; 286,97</t>
+          <t>-49,62; 444,69</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-72,97; 204,55</t>
+          <t>-84,16; 193,31</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-36,79; 385,56</t>
+          <t>-65,78; 318,57</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-26,44; 199,02</t>
+          <t>-31,69; 191,99</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-62,56; 81,73</t>
+          <t>-63,33; 80,18</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-28,36; 215,81</t>
+          <t>-23,32; 238,61</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0,36</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0,35</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0,25</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-2,23</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-1,11</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-3,5</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0,36</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0,35</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>-3,51</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-1,5</t>
+          <t>-1,43</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 1,0</t>
+          <t>-2,92; 4,08</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 3,14</t>
+          <t>-3,16; 3,67</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,02; -0,41</t>
+          <t>-3,35; 3,48</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 3,87</t>
+          <t>-6,17; 1,7</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 3,57</t>
+          <t>-5,61; 3,32</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 3,38</t>
+          <t>-8,0; -0,19</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 1,71</t>
+          <t>-3,44; 1,57</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 2,91</t>
+          <t>-2,82; 2,38</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 0,94</t>
+          <t>-4,03; 0,9</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>13,5%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>13,24%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>9,39%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-46,41%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-23,1%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-72,95%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>13,5%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>13,24%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>-73,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-41,32%</t>
+          <t>-39,47%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-90,78; 53,49</t>
+          <t>-79,58; 443,12</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-83,49; 122,67</t>
+          <t>-75,07; 384,95</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 94,44</t>
+          <t>-78,84; 336,59</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-74,04; 418,77</t>
+          <t>-85,97; 138,95</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-71,08; 421,85</t>
+          <t>-80,16; 134,3</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-82,22; 332,62</t>
+          <t>-100,0; 37,44</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-68,65; 89,61</t>
+          <t>-68,86; 72,0</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-55,1; 161,69</t>
+          <t>-59,99; 114,68</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-79,92; 52,27</t>
+          <t>-75,76; 47,16</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>0,95</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>0,17</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>4,59</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>-2,16</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>1,8</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-1,59</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>0,95</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>0,17</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,26</t>
+          <t>-1,68</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1,89</t>
+          <t>1,41</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 0,0</t>
+          <t>-1,8; 4,78</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 6,91</t>
+          <t>-1,81; 3,28</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 0,58</t>
+          <t>0,46; 10,9</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 4,72</t>
+          <t>-7,73; 0,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 3,39</t>
+          <t>-2,82; 7,18</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,94; 12,67</t>
+          <t>-7,22; 0,49</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 1,59</t>
+          <t>-3,0; 1,63</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 3,69</t>
+          <t>-1,84; 3,61</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 5,53</t>
+          <t>-1,3; 5,21</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>104,67%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>18,34%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>508,04%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>83,32%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-73,74%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>104,67%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>18,34%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>582,53%</t>
+          <t>-77,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>122,2%</t>
+          <t>91,25%</t>
         </is>
       </c>
     </row>
@@ -1898,12 +1898,12 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-87,39; 756,45</t>
+          <t>-82,47; —</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 928,13</t>
+          <t>-79,99; 1222,42</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-0,17</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>0,09</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>0,8</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>-1,13</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>-0,85</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-0,88</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-0,17</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>0,09</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,01</t>
+          <t>-0,67</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,12</t>
+          <t>0,1</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 0,24</t>
+          <t>-1,58; 1,17</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 0,47</t>
+          <t>-1,24; 1,44</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 0,57</t>
+          <t>-0,93; 2,48</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 1,21</t>
+          <t>-2,5; 0,39</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 1,45</t>
+          <t>-2,25; 0,59</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 3,0</t>
+          <t>-2,08; 0,96</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 0,25</t>
+          <t>-1,59; 0,31</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 0,66</t>
+          <t>-1,4; 0,51</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 1,31</t>
+          <t>-0,92; 1,35</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-6,59%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>3,6%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>30,59%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>-37,54%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>-28,28%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-29,02%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-6,59%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>3,6%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>-22,2%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-64,76; 14,0</t>
+          <t>-47,06; 60,47</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-61,14; 23,54</t>
+          <t>-38,7; 76,57</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-61,41; 29,86</t>
+          <t>-27,87; 130,72</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-48,2; 61,32</t>
+          <t>-65,64; 18,81</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-39,94; 74,22</t>
+          <t>-60,68; 33,81</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-21,24; 151,54</t>
+          <t>-54,9; 49,29</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-48,68; 8,92</t>
+          <t>-48,28; 14,42</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-41,46; 29,76</t>
+          <t>-40,96; 22,51</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-28,58; 59,73</t>
+          <t>-28,89; 59,93</t>
         </is>
       </c>
     </row>
